--- a/exemples/Saisies_Production_exemple.xlsx
+++ b/exemples/Saisies_Production_exemple.xlsx
@@ -147,7 +147,7 @@
     <t>Marc Le Gall</t>
   </si>
   <si>
-    <t>OP1042</t>
+    <t>10425</t>
   </si>
   <si>
     <t>Granulés Nutri-Algue</t>
@@ -195,7 +195,7 @@
     <t>Sophie Tanguy</t>
   </si>
   <si>
-    <t>OP1187</t>
+    <t>11873</t>
   </si>
   <si>
     <t>L229572</t>
@@ -228,7 +228,7 @@
     <t>Yann Kerhervé</t>
   </si>
   <si>
-    <t>OP1256</t>
+    <t>02561</t>
   </si>
   <si>
     <t>Quantite_Recue_kg=5400 (Dépassement validé par le chef d’équipe — lot suivi en qualité.)</t>
@@ -336,7 +336,7 @@
     <t>Nadia Bouchard</t>
   </si>
   <si>
-    <t>OP1301</t>
+    <t>13017</t>
   </si>
   <si>
     <t>Edouard Vasse</t>
